--- a/naver-place-crawler/results_derma/북구_피부과.xlsx
+++ b/naver-place-crawler/results_derma/북구_피부과.xlsx
@@ -1294,10 +1294,10 @@
         <v>2273</v>
       </c>
       <c r="Q9" t="n">
-        <v>5677</v>
+        <v>5684</v>
       </c>
       <c r="R9" t="n">
-        <v>7950</v>
+        <v>7957</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>dzet9797@naver.com</t>
+          <t>fybs6986@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -1573,13 +1573,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="Q12" t="n">
         <v>101</v>
       </c>
       <c r="R12" t="n">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1764,10 +1764,10 @@
         <v>2685</v>
       </c>
       <c r="Q14" t="n">
-        <v>6265</v>
+        <v>6275</v>
       </c>
       <c r="R14" t="n">
-        <v>8950</v>
+        <v>8960</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -2050,10 +2050,10 @@
         <v>3648</v>
       </c>
       <c r="Q17" t="n">
-        <v>5203</v>
+        <v>5218</v>
       </c>
       <c r="R17" t="n">
-        <v>8851</v>
+        <v>8866</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>beautynyoung00@naver.com</t>
+          <t>rizdaheeo0o@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -3084,10 +3084,10 @@
         <v>497</v>
       </c>
       <c r="Q28" t="n">
-        <v>2320</v>
+        <v>2324</v>
       </c>
       <c r="R28" t="n">
-        <v>2817</v>
+        <v>2821</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -5806,10 +5806,10 @@
         <v>950</v>
       </c>
       <c r="Q57" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="R57" t="n">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>

--- a/naver-place-crawler/results_derma/북구_피부과.xlsx
+++ b/naver-place-crawler/results_derma/북구_피부과.xlsx
@@ -1098,10 +1098,10 @@
         <v>871</v>
       </c>
       <c r="Q7" t="n">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="R7" t="n">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1291,13 +1291,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2273</v>
+        <v>2270</v>
       </c>
       <c r="Q9" t="n">
-        <v>5684</v>
+        <v>5689</v>
       </c>
       <c r="R9" t="n">
-        <v>7957</v>
+        <v>7959</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1764,10 +1764,10 @@
         <v>2685</v>
       </c>
       <c r="Q14" t="n">
-        <v>6275</v>
+        <v>6282</v>
       </c>
       <c r="R14" t="n">
-        <v>8960</v>
+        <v>8967</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -2050,10 +2050,10 @@
         <v>3648</v>
       </c>
       <c r="Q17" t="n">
-        <v>5218</v>
+        <v>5220</v>
       </c>
       <c r="R17" t="n">
-        <v>8866</v>
+        <v>8868</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2144,10 +2144,10 @@
         <v>825</v>
       </c>
       <c r="Q18" t="n">
-        <v>1191</v>
+        <v>1199</v>
       </c>
       <c r="R18" t="n">
-        <v>2016</v>
+        <v>2024</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2181,11 +2181,7 @@
           <t>리쥬엘의원 동성로</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>rejuel_beauty@naver.com</t>
-        </is>
-      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
@@ -2235,13 +2231,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="Q19" t="n">
         <v>26</v>
       </c>
       <c r="R19" t="n">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2557,11 +2553,7 @@
           <t>동산이피부과의원</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>dsmc7551@naver.com</t>
-        </is>
-      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
@@ -2896,10 +2888,10 @@
         <v>2402</v>
       </c>
       <c r="Q26" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="R26" t="n">
-        <v>2442</v>
+        <v>2441</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -3837,13 +3829,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2320</v>
+        <v>2321</v>
       </c>
       <c r="Q36" t="n">
         <v>506</v>
       </c>
       <c r="R36" t="n">
-        <v>2826</v>
+        <v>2827</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3968,39 +3960,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>유아미의원</t>
+          <t>미즈피부과의원</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>youamiclinic@naver.com</t>
+          <t>chair0629@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>053-743-3300</t>
+          <t>0507-1338-8275</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>대구광역시 수성구 화랑로 56 효창빌딩 2층</t>
+          <t>대구광역시 북구 침산남로 154 3층</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/youamiclinic</t>
+          <t>http://www.mizskin.com/</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -4016,7 +4008,7 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -4025,13 +4017,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>219</v>
+        <v>1149</v>
       </c>
       <c r="Q38" t="n">
-        <v>26</v>
+        <v>221</v>
       </c>
       <c r="R38" t="n">
-        <v>245</v>
+        <v>1370</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4040,12 +4032,12 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>604184016</t>
+          <t>12006789</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/604184016</t>
+          <t>https://m.place.naver.com/place/12006789</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -4062,44 +4054,40 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>미즈피부과의원</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>chair0629@naver.com</t>
-        </is>
-      </c>
+          <t>참고운피부과의원</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1338-8275</t>
+          <t>053-944-7701</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산남로 154 3층</t>
+          <t>대구광역시 동구 신암남로 183</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>http://www.mizskin.com/</t>
+          <t>http://www.okskin.co.kr</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4110,7 +4098,7 @@
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -4119,13 +4107,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1149</v>
+        <v>457</v>
       </c>
       <c r="Q39" t="n">
-        <v>221</v>
+        <v>9</v>
       </c>
       <c r="R39" t="n">
-        <v>1370</v>
+        <v>466</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4134,12 +4122,12 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>12006789</t>
+          <t>12878108</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12006789</t>
+          <t>https://m.place.naver.com/place/12878108</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -4156,29 +4144,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>참고운피부과의원</t>
+          <t>대구동성로 예쁨주의쁨의원</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>cgederma7@naver.com</t>
+          <t>qwe8349@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>053-944-7701</t>
+          <t>053-716-3996</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>대구광역시 동구 신암남로 183</t>
+          <t>대구광역시 중구 동성로 39 5,6층</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>http://www.okskin.co.kr</t>
+          <t>http://www.ppeum26.com/</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4204,22 +4192,22 @@
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>457</v>
+        <v>4877</v>
       </c>
       <c r="Q40" t="n">
-        <v>9</v>
+        <v>93</v>
       </c>
       <c r="R40" t="n">
-        <v>466</v>
+        <v>4970</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4228,12 +4216,12 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>12878108</t>
+          <t>1600113316</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12878108</t>
+          <t>https://m.place.naver.com/place/1600113316</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4245,34 +4233,30 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>피부과</t>
+          <t>병원,의원</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>대구동성로 예쁨주의쁨의원</t>
+          <t>필피부과비뇨기과</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>qwe8349@naver.com</t>
+          <t>hwangh6293@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>053-716-3996</t>
-        </is>
-      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>대구광역시 중구 동성로 39 5,6층</t>
+          <t>대구광역시 북구 침산로 144</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>http://www.ppeum26.com/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4282,7 +4266,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -4298,22 +4282,22 @@
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>4877</v>
+        <v>6</v>
       </c>
       <c r="Q41" t="n">
-        <v>93</v>
+        <v>3</v>
       </c>
       <c r="R41" t="n">
-        <v>4970</v>
+        <v>9</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4322,12 +4306,12 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1600113316</t>
+          <t>16334077</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1600113316</t>
+          <t>https://m.place.naver.com/place/16334077</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -4339,40 +4323,44 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>병원,의원</t>
+          <t>피부과</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>필피부과비뇨기과</t>
+          <t>폼의원</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>hwangh6293@naver.com</t>
+          <t>baeyj8454@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0507-1312-7799</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>대구광역시 북구 침산로 144</t>
+          <t>대구광역시 중구 달구벌대로 2141 3층</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://pf.kakao.com/_jHxhfxl/friend</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -4388,22 +4376,22 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>6</v>
+        <v>311</v>
       </c>
       <c r="Q42" t="n">
-        <v>3</v>
+        <v>98</v>
       </c>
       <c r="R42" t="n">
-        <v>9</v>
+        <v>409</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4412,12 +4400,12 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>16334077</t>
+          <t>1394815021</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/16334077</t>
+          <t>https://m.place.naver.com/place/1394815021</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -4434,34 +4422,34 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>폼의원</t>
+          <t>미강의원</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>baeyj8454@naver.com</t>
+          <t>migangskin@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1312-7799</t>
+          <t>053-955-8575</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>대구광역시 중구 달구벌대로 2141 3층</t>
+          <t>대구광역시 북구 동북로 170 3층</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_jHxhfxl/friend</t>
+          <t>https://blog.naver.com/migangskin</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4471,7 +4459,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4482,22 +4470,22 @@
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>311</v>
+        <v>166</v>
       </c>
       <c r="Q43" t="n">
-        <v>98</v>
+        <v>31</v>
       </c>
       <c r="R43" t="n">
-        <v>409</v>
+        <v>197</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4506,12 +4494,12 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1394815021</t>
+          <t>1874632628</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1394815021</t>
+          <t>https://m.place.naver.com/place/1874632628</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -4528,34 +4516,34 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>미강의원</t>
+          <t>나비피부과의원</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>migangskin@naver.com</t>
+          <t>skqlvlqn07@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>053-955-8575</t>
+          <t>0507-1433-7586</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>대구광역시 북구 동북로 170 3층</t>
+          <t>대구광역시 중구 달구벌대로 2179 9층</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/migangskin</t>
+          <t>https://nabiskin.com</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4565,7 +4553,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4581,17 +4569,17 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>166</v>
+        <v>208</v>
       </c>
       <c r="Q44" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="R44" t="n">
-        <v>197</v>
+        <v>246</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4600,12 +4588,12 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1874632628</t>
+          <t>12069077</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1874632628</t>
+          <t>https://m.place.naver.com/place/12069077</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -5377,11 +5365,7 @@
           <t>뮤즈의원 대구점</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>musegeomdan@naver.com</t>
-        </is>
-      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
@@ -5659,11 +5643,7 @@
           <t>가톨릭피부과의원입구</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>lik8540@naver.com</t>
-        </is>
-      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
@@ -5843,11 +5823,7 @@
           <t>참피부과의원</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>moekjirong76@naver.com</t>
-        </is>
-      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
@@ -6125,11 +6101,7 @@
           <t>가톨릭피부과의원입원병동</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>xssm12@naver.com</t>
-        </is>
-      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
@@ -6215,11 +6187,7 @@
           <t>더퍼스트피부과의원</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>firstderma@naver.com</t>
-        </is>
-      </c>
+      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
@@ -6272,10 +6240,10 @@
         <v>639</v>
       </c>
       <c r="Q62" t="n">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="R62" t="n">
-        <v>1647</v>
+        <v>1648</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6309,11 +6277,7 @@
           <t>가톨릭피부과의원</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>kym7729@naver.com</t>
-        </is>
-      </c>
+      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
@@ -6403,11 +6367,7 @@
           <t>신피부과의원</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>dermashin1960@naver.com</t>
-        </is>
-      </c>
+      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
@@ -6689,11 +6649,7 @@
           <t>한국한센복지협회 대구경북지부부설 복지피부과의원</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>mademe7@naver.com</t>
-        </is>
-      </c>
+      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
@@ -6934,10 +6890,10 @@
         <v>5610</v>
       </c>
       <c r="Q69" t="n">
-        <v>1817</v>
+        <v>1819</v>
       </c>
       <c r="R69" t="n">
-        <v>7427</v>
+        <v>7429</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -7159,11 +7115,7 @@
           <t>신세계의원</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>dugod16@naver.com</t>
-        </is>
-      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
@@ -7253,11 +7205,7 @@
           <t>루센트셀연합의원</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>soso_flower_@naver.com</t>
-        </is>
-      </c>
+      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
@@ -7347,11 +7295,7 @@
           <t>강창수비뇨기과의원</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>binterest@naver.com</t>
-        </is>
-      </c>
+      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
